--- a/00_Documentos/Informes y avances/Categorias_datos_y_nuevas_fuentes.xlsx
+++ b/00_Documentos/Informes y avances/Categorias_datos_y_nuevas_fuentes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\Laboral\EAFIT\Valor Público\2026\Provincias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\Laboral\EAFIT\Valor Público\2026\Provincias\Informes y avances\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1F1B6F-E5FC-4F63-A034-D211ADFE0B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CFC0FB-73CF-4D73-B6F7-724B129F353E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1EFA439D-C600-4CE7-92D6-FC031D2B74FC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1EFA439D-C600-4CE7-92D6-FC031D2B74FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Propuesta categorizacion datos" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="348">
   <si>
     <t>Educación</t>
   </si>
@@ -1006,12 +1006,154 @@
   <si>
     <t>Secretaría de Agricultura de Antioquia, gremios lácteos (Fedegán) y tableros del SIASAR</t>
   </si>
+  <si>
+    <t>Área sembrada cultivos transitorios en el periodo de referencia</t>
+  </si>
+  <si>
+    <t>Área cosechada, producción y rendimiento en el periodo de referencia de los cultivos transitorios</t>
+  </si>
+  <si>
+    <t>Área cultivada, cosechada, producción y rendimiento de cultivos permanentes</t>
+  </si>
+  <si>
+    <t>Áreas ocupadas en forrajes, pastos de corte y silvopastoriles</t>
+  </si>
+  <si>
+    <t>Inventario de especies pecuarias</t>
+  </si>
+  <si>
+    <t>Resultados a nivel municipal y semestral. Ültima observación 2025.{
+https://upra.gov.co/es-co/eva/eva-2025</t>
+  </si>
+  <si>
+    <t>Resultados a nivel municipal y semestral. Ültima observación 2025.{
+https://upra.gov.co/es-co/eva/eva-2026</t>
+  </si>
+  <si>
+    <t>Resultados a nivel municipal y semestral. Ültima observación 2025.{
+https://upra.gov.co/es-co/eva/eva-2027</t>
+  </si>
+  <si>
+    <t>Resultados a nivel municipal y semestral. Ültima observación 2025.{
+https://upra.gov.co/es-co/eva/eva-2028</t>
+  </si>
+  <si>
+    <t>Resultados a nivel municipal y semestral. Ültima observación 2025.{
+https://upra.gov.co/es-co/eva/eva-2029</t>
+  </si>
+  <si>
+    <t>EVA 2025 - UPRA</t>
+  </si>
+  <si>
+    <t>Existencia de una Mesa Local de Turismo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mesas Locales de Turismo en Colombia son espacios de articulación entre actores públicos, privados y comunitarios, diseñados para planificar, promover y gestionar el desarrollo turístico sostenible y competitivo a nivel municipal</t>
+  </si>
+  <si>
+    <t>Identificación individual municipal. Se supone que los datos están disponibles para descargar en excel pero no funcionaba el enlace cuando en fecha de consulta (04-14)
+https://secretaria.turismoantioquia.travel/estado-de-instrumentos-de-planificacion-turistica-en-antioquia/</t>
+  </si>
+  <si>
+    <t>SITA Observatorio de Turismo Sostenible de Antioquia - Gobernación de Antioquia</t>
+  </si>
+  <si>
+    <t>Mesa Local de Turismo Formalizada</t>
+  </si>
+  <si>
+    <t>Registro de la mesa de turismo en instrumentos oficiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventario turístico realizado </t>
+  </si>
+  <si>
+    <t>Registro de inventario turístico o realización en proceso.Es el registro ordenado de atractivos físicos y culturales, gestionado por el MINCIT para planificar, potenciar destinos y tomar decisiones en el sector público/privado</t>
+  </si>
+  <si>
+    <t>Existencia de un Plan Local de Turismo</t>
+  </si>
+  <si>
+    <t>Plan Local de Turismo realizado o en proceso. Es una herramienta de planeamiento y regulación para el desarrollo del turismo.</t>
+  </si>
+  <si>
+    <t>Plan local de turismo formalizado mediante acto adminsitrativo</t>
+  </si>
+  <si>
+    <t>Estado del Instrumento de Ordenamiento Territorial</t>
+  </si>
+  <si>
+    <t>Identificación individual municipal. Se supone que los datos están disponibles para descargar en excel pero no funcionaba el enlace cuando en fecha de consulta (04-14)
+No se explica exactamente a qué instrumento hace referencia.
+https://secretaria.turismoantioquia.travel/estado-de-instrumentos-de-planificacion-turistica-en-antioquia/</t>
+  </si>
+  <si>
+    <t>Cifras turísticas territoriales</t>
+  </si>
+  <si>
+    <t>Beterías de indicadores turísticos en dimensiones económica, ambiental y social</t>
+  </si>
+  <si>
+    <t>Estadisticas de pleaneación turística</t>
+  </si>
+  <si>
+    <t>Estadísticas del mercado turístico</t>
+  </si>
+  <si>
+    <t>PREFERENCIAS DE VIAJE DE LOS TURISTAS ANTIOQUEÑOS - 2023</t>
+  </si>
+  <si>
+    <t>Resultados de encuestas a turistas</t>
+  </si>
+  <si>
+    <t>No se realiza identificación individual de los indicadores. Para fecha de consulta es posible descargar los datos en excel (04-14)
+https://secretaria.turismoantioquia.travel/cifras-turisticas-regionales/</t>
+  </si>
+  <si>
+    <t>No se realiza identificación individual de los indicadores. Para fecha de consulta es posible descargar los datos en excel (04-14)
+https://secretaria.turismoantioquia.travel/estado-de-instrumentos-de-planificacion-turistica-en-antioquia-2/</t>
+  </si>
+  <si>
+    <t>Predios con buenas prácticas agrícolas</t>
+  </si>
+  <si>
+    <t>Certificación del ICA en sostenibilidad del ejercicio agrícola.</t>
+  </si>
+  <si>
+    <t>Certificaciones individualizadas</t>
+  </si>
+  <si>
+    <t>Disponible a nivel de predio, con datos de identificación del municipio, área y tipo de cultivo.
+https://www.datos.gov.co/Agricultura-y-Desarrollo-Rural/LISTA-VIGENTE-DE-PREDIOS-CERTIFICADOS-Y-RECERTIFIC/wusb-7b8z/about_data</t>
+  </si>
+  <si>
+    <t>SIASAR</t>
+  </si>
+  <si>
+    <t>Es un sistema internacional de información de sistema hidrográfico, comunidades, salud, sostenibilidad alrededor del agua. Puede contener información interesante pero a primera vista no veo buena covertura de información de sistema hidrográfico para Antioquia.
+https://colombia.siasar.org/es</t>
+  </si>
+  <si>
+    <t>Estado del sistema hidrográfico</t>
+  </si>
+  <si>
+    <t>Caracterización del sector y mercado ganadero</t>
+  </si>
+  <si>
+    <t>Fedegán</t>
+  </si>
+  <si>
+    <t>Tienen una serie de bases de datos nacionales e internacionales pero no encontré nada que vaya al nivel municipal.
+https://www.fedegan.org.co/estadisticas/general</t>
+  </si>
+  <si>
+    <t>ICA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1062,6 +1204,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1089,7 +1237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1134,14 +1282,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4427,72 +4584,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="19" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>298</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>302</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="19" t="s">
         <v>304</v>
       </c>
     </row>
@@ -4503,7 +4660,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46747B2C-05C1-4320-8F4F-A325FE012676}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.42578125" bestFit="1" customWidth="1"/>
@@ -4515,15 +4672,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -4549,7 +4706,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="20" t="s">
         <v>214</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -4567,12 +4724,14 @@
       <c r="F3" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="22" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
+      <c r="A4" s="20" t="s">
+        <v>214</v>
+      </c>
       <c r="B4" s="7" t="s">
         <v>269</v>
       </c>
@@ -4588,10 +4747,12 @@
       <c r="F4" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G4" s="17"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="5" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
+      <c r="A5" s="20" t="s">
+        <v>214</v>
+      </c>
       <c r="B5" s="7" t="s">
         <v>269</v>
       </c>
@@ -4607,10 +4768,12 @@
       <c r="F5" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G5" s="17"/>
+      <c r="G5" s="22"/>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
+      <c r="A6" s="20" t="s">
+        <v>214</v>
+      </c>
       <c r="B6" s="7" t="s">
         <v>269</v>
       </c>
@@ -4626,10 +4789,12 @@
       <c r="F6" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G6" s="17"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
+      <c r="A7" s="20" t="s">
+        <v>214</v>
+      </c>
       <c r="B7" s="7" t="s">
         <v>269</v>
       </c>
@@ -4645,10 +4810,12 @@
       <c r="F7" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G7" s="17"/>
+      <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
+      <c r="A8" s="20" t="s">
+        <v>214</v>
+      </c>
       <c r="B8" s="7" t="s">
         <v>269</v>
       </c>
@@ -4664,7 +4831,7 @@
       <c r="F8" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G8" s="17"/>
+      <c r="G8" s="22"/>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -4706,61 +4873,409 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C27" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E27" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F27" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G27" s="14" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D12" s="9"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D13" s="9"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D14" s="9"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D15" s="9"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D16" s="9"/>
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D19" s="9"/>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D28" s="9"/>
+      <c r="G28" s="14"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D29" s="9"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D30" s="9"/>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D31" s="9"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D32" s="9"/>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D34" s="9"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:A8"/>
+  <mergeCells count="2">
     <mergeCell ref="G3:G8"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/00_Documentos/Informes y avances/Categorias_datos_y_nuevas_fuentes.xlsx
+++ b/00_Documentos/Informes y avances/Categorias_datos_y_nuevas_fuentes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\Laboral\EAFIT\Valor Público\2026\Provincias\Informes y avances\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CFC0FB-73CF-4D73-B6F7-724B129F353E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9535E87-480C-4EEF-B2D7-4760E5897687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1EFA439D-C600-4CE7-92D6-FC031D2B74FC}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="361">
   <si>
     <t>Educación</t>
   </si>
@@ -1148,12 +1148,53 @@
   <si>
     <t>ICA</t>
   </si>
+  <si>
+    <t>Presencia de cultivos de coca</t>
+  </si>
+  <si>
+    <t>Area total cultivada</t>
+  </si>
+  <si>
+    <t>Observatorio de Drogas de Colombia 2023</t>
+  </si>
+  <si>
+    <t>Tienen series anualizadas por municipio. Podemos sacar un % de cambio por ejemplo para el periodo de 10 años o 5 años anteriores y es un buen dato para analizar.
+https://sidco.odc.gov.co/ReporPoliticaDroga/Default?reportName=005_Presencia_cultivos_coca</t>
+  </si>
+  <si>
+    <t>Seguridad, Justicia y Paz</t>
+  </si>
+  <si>
+    <t>Capturas por delitos relacionados con drogas</t>
+  </si>
+  <si>
+    <t>Numero de capturas total o por delito y por municipios</t>
+  </si>
+  <si>
+    <t>observatorio de drogas de colombia 2025</t>
+  </si>
+  <si>
+    <t>https://sidco.odc.gov.co/ReporPoliticaDroga/Default?reportName=009_Capturas</t>
+  </si>
+  <si>
+    <t>Total anual de delitos por categoría</t>
+  </si>
+  <si>
+    <t>Seguimiento a 11 delitos por municipio y año, además de modalidades específicas</t>
+  </si>
+  <si>
+    <t>Policía nacional 2025</t>
+  </si>
+  <si>
+    <t>Están de 2020-2025 en "Cuadro de salida histórico delictivo 2020-2025"
+https://www.policia.gov.co/estadistica-delictiva</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1210,6 +1251,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1234,10 +1283,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1297,11 +1347,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4672,15 +4729,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -4724,7 +4781,7 @@
       <c r="F3" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="23" t="s">
         <v>266</v>
       </c>
     </row>
@@ -4747,7 +4804,7 @@
       <c r="F4" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G4" s="22"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
@@ -4768,7 +4825,7 @@
       <c r="F5" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G5" s="22"/>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
@@ -4789,7 +4846,7 @@
       <c r="F6" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
@@ -4810,7 +4867,7 @@
       <c r="F7" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
@@ -4831,7 +4888,7 @@
       <c r="F8" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G8" s="22"/>
+      <c r="G8" s="23"/>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -5241,17 +5298,74 @@
         <v>275</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D28" s="9"/>
-      <c r="G28" s="14"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D29" s="9"/>
-      <c r="G29" s="14"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D30" s="9"/>
-      <c r="G30" s="14"/>
+    <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D31" s="9"/>
@@ -5276,7 +5390,10 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G29" r:id="rId1" xr:uid="{0AE8D685-3E25-4761-AF36-2FAF602E6B66}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>